--- a/CHESS_rubble_mound_inputs.xlsx
+++ b/CHESS_rubble_mound_inputs.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\StormSim_Library\PSE_Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\CHESS-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70224E68-1741-4C42-B63A-DDA2F043F3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D6FF3C-A6D6-446E-BBD9-EF165F34B842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="4665" windowWidth="28800" windowHeight="15270" xr2:uid="{DF680589-5370-4D92-A3AE-D910B140CCC4}"/>
+    <workbookView xWindow="5325" yWindow="5325" windowWidth="28800" windowHeight="15270"/>
   </bookViews>
   <sheets>
     <sheet name="Rubblemound" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -531,48 +531,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -729,97 +729,99 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <protection locked="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <protection locked="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <protection locked="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <protection locked="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <protection locked="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1138,17 +1140,17 @@
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="101.7109375" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="153.42578125" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
-    <col min="7" max="7" width="84.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="101.7109375" customWidth="true"/>
+    <col min="2" max="2" width="53.5703125" customWidth="true"/>
+    <col min="3" max="3" width="19.28515625" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="63" customWidth="true"/>
+    <col min="6" max="6" width="45" customWidth="true"/>
+    <col min="7" max="7" width="84.28515625" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="46.140625" customWidth="true"/>
+    <col min="9" max="9" width="13.5703125" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>131</v>
       </c>
@@ -1162,7 +1164,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>18</v>
       </c>
@@ -1188,7 +1190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>130</v>
       </c>
@@ -1214,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>127</v>
       </c>
@@ -1240,7 +1242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>124</v>
       </c>
@@ -1266,7 +1268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>121</v>
       </c>
@@ -1292,7 +1294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>118</v>
       </c>
@@ -1318,7 +1320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>115</v>
       </c>
@@ -1344,7 +1346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>112</v>
       </c>
@@ -1370,7 +1372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>110</v>
       </c>
@@ -1396,7 +1398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>108</v>
       </c>
@@ -1422,7 +1424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>105</v>
       </c>
@@ -1433,14 +1435,14 @@
         <v>44</v>
       </c>
       <c r="D12" s="2">
-        <v>176.45</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>103</v>
       </c>
@@ -1464,7 +1466,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>101</v>
       </c>
@@ -1490,7 +1492,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>99</v>
       </c>
@@ -1516,7 +1518,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>95</v>
       </c>
@@ -1542,7 +1544,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>93</v>
       </c>
@@ -1560,7 +1562,7 @@
       <c r="H17" s="38"/>
       <c r="I17" s="38"/>
     </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>89</v>
       </c>
@@ -1580,7 +1582,7 @@
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
     </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>84</v>
       </c>
@@ -1606,7 +1608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>81</v>
       </c>
@@ -1632,7 +1634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" x14ac:dyDescent="0.25">
       <c r="A21" s="36"/>
       <c r="B21" s="35"/>
       <c r="C21" s="34"/>
@@ -1650,7 +1652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A22" s="33" t="s">
         <v>77</v>
       </c>
@@ -1670,7 +1672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>18</v>
       </c>
@@ -1696,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>71</v>
       </c>
@@ -1722,7 +1724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>137</v>
       </c>
@@ -1740,7 +1742,7 @@
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
     </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>63</v>
       </c>
@@ -1760,7 +1762,7 @@
       <c r="H26" s="30"/>
       <c r="I26" s="30"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>58</v>
       </c>
@@ -1786,7 +1788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" x14ac:dyDescent="0.25">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
@@ -1804,7 +1806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>55</v>
       </c>
@@ -1824,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>18</v>
       </c>
@@ -1838,7 +1840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
         <v>54</v>
       </c>
@@ -1852,7 +1854,7 @@
         <v>180.1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>52</v>
       </c>
@@ -1866,7 +1868,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>50</v>
       </c>
@@ -1880,7 +1882,7 @@
         <v>176.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>48</v>
       </c>
@@ -1894,7 +1896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>46</v>
       </c>
@@ -1908,7 +1910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>140</v>
       </c>
@@ -1922,7 +1924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
         <v>142</v>
       </c>
@@ -1936,13 +1938,13 @@
         <v>173.99</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
     </row>
-    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>43</v>
       </c>
@@ -1950,7 +1952,7 @@
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
     </row>
-    <row r="40" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>18</v>
       </c>
@@ -1964,7 +1966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1980,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
@@ -1992,7 +1994,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
@@ -2006,7 +2008,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>35</v>
       </c>
@@ -2020,7 +2022,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>32</v>
       </c>
@@ -2034,7 +2036,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>29</v>
       </c>
@@ -2048,7 +2050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>27</v>
       </c>
@@ -2062,7 +2064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>25</v>
       </c>
@@ -2076,7 +2078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>23</v>
       </c>
@@ -2090,7 +2092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" ht="60.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A50" s="17" t="s">
         <v>21</v>
       </c>
@@ -2104,17 +2106,17 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
     </row>
-    <row r="53" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="true" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15" customHeight="true" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="19.5" customHeight="true" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection formatColumns="0" selectLockedCells="1"/>
+  <sheetProtection formatColumns="false" selectLockedCells="true"/>
   <protectedRanges>
     <protectedRange sqref="I15:I16 I20:I21 I23:I24 I28" name="Range1_1"/>
     <protectedRange sqref="D50 D41:D45" name="Range1_1_4"/>
